--- a/public/inputs/y07-english - input.xlsx
+++ b/public/inputs/y07-english - input.xlsx
@@ -444,7 +444,6 @@
           <t>Unit 1 · Adventure</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -457,7 +456,6 @@
           <t>Discuss the features of adventure stories / look for explicit information in a text/ explore how writers structure theire stories.</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -470,7 +468,6 @@
           <t>Exam revision 1</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -483,7 +480,6 @@
           <t>Describe how stories develop/ Explore the features of monologue/ Write and perform a monologue.</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -496,7 +492,6 @@
           <t>Explore ways of using speech to engage an audience/ look for implicit meaning on a text/ Use different sentence types to add interest to descritive writing.</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -509,7 +504,6 @@
           <t>Look for explicit and implicit meanings in poetry/ Explore how poets use the languge features of effect/ Learn how to writ an anlysis of a poem.</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -522,7 +516,6 @@
           <t>Investigate some features of suspense writing/ Explore the effects of language and grammatical choices/ read aloud with expression.</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -535,7 +528,6 @@
           <t>Use planning techniques for a piece of narrative writing</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -548,7 +540,6 @@
           <t>Check your progress 1</t>
         </is>
       </c>
-      <c r="C10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -561,7 +552,6 @@
           <t>Practice Exam 1</t>
         </is>
       </c>
-      <c r="C11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -574,7 +564,6 @@
           <t>Exam 1</t>
         </is>
       </c>
-      <c r="C12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -587,7 +576,6 @@
           <t>Unit 2 · Hey, You Down There</t>
         </is>
       </c>
-      <c r="C13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -600,7 +588,6 @@
           <t>Explore How a writer presents characters and relationships/ Lear how a writer positions a character in a text/ Understand the function of a sentence openings.</t>
         </is>
       </c>
-      <c r="C14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -613,7 +600,6 @@
           <t>Learn about compound-complex sentences/ Explore techniques used whwn writing and performing spoken drama/ Assess your own speaking and performance skills.</t>
         </is>
       </c>
-      <c r="C15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -626,7 +612,6 @@
           <t>Explore the social and historical context of ?Hey, You DownThers'/ Understand how non- standard English helps to convey character/ practise your group discussion skills/</t>
         </is>
       </c>
-      <c r="C16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -639,7 +624,6 @@
           <t>Learn how writers show character through languages choises/ Explore formal and informal language/ consider vocabulary for effect.</t>
         </is>
       </c>
-      <c r="C17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -652,7 +636,6 @@
           <t>Explore how a writer controls information in a text/ use your scanning skills to find information in a text/ understand how writers use characters to convey themes and ideas.</t>
         </is>
       </c>
-      <c r="C18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -665,7 +648,6 @@
           <t>Reat the ending of a story/ Explore how a writer prepares the reader for a story ending/ Plan and produce a sequenced short story.</t>
         </is>
       </c>
-      <c r="C19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -678,7 +660,6 @@
           <t>Check your progress 2</t>
         </is>
       </c>
-      <c r="C20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -691,7 +672,6 @@
           <t>Exam review 2</t>
         </is>
       </c>
-      <c r="C21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -704,7 +684,6 @@
           <t>Practice Exam 2</t>
         </is>
       </c>
-      <c r="C22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -717,7 +696,6 @@
           <t>Exam 2</t>
         </is>
       </c>
-      <c r="C23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -730,7 +708,6 @@
           <t>Unit 3 · Film and fame</t>
         </is>
       </c>
-      <c r="C24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -743,7 +720,6 @@
           <t>Explore how a writer uses language to establish a setting/ consider how a writer shapes the resder's opinion about a character/ investigate the different features of spoken English and written English.</t>
         </is>
       </c>
-      <c r="C25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -756,7 +732,6 @@
           <t>Plan ideas to develop a fiction story/ Use features of Informal English in direct speech/ write about a specific place using a range of nouns.</t>
         </is>
       </c>
-      <c r="C26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -769,7 +744,6 @@
           <t>Investigate the techniques used by jounalists to write headlines/ explore the structural features of a newspaper arcticl/ Consider the language features of a factual information article</t>
         </is>
       </c>
-      <c r="C27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -782,7 +756,6 @@
           <t>Investigate thestructural features of a film review./ Explore the way writers use language to establish the style of a journalistic review/ Consider how descriptive language can be used to convey.</t>
         </is>
       </c>
-      <c r="C28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -795,7 +768,6 @@
           <t>Reserach and plan the content of a film revew.</t>
         </is>
       </c>
-      <c r="C29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -808,7 +780,6 @@
           <t>Understand explicit and implicit information in a text/ Listen and respond to a news story/ Explore ways of planing, writing and delivering a persuasive speech.</t>
         </is>
       </c>
-      <c r="C30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -821,7 +792,6 @@
           <t>Check your progress 3</t>
         </is>
       </c>
-      <c r="C31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -834,7 +804,6 @@
           <t>Unit 4 · Small but perfect</t>
         </is>
       </c>
-      <c r="C32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -847,7 +816,6 @@
           <t>Learn about the genre of flash fiction/ Explore symbols and images in a text/ analyse how a writer uses symbols and images for effect.</t>
         </is>
       </c>
-      <c r="C33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -860,7 +828,6 @@
           <t>Create a fictional history about an object/ Explore the use of time connectives in sequencing creative writing./ Build descriptions through expanded noun and verb phrases.</t>
         </is>
       </c>
-      <c r="C34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -873,7 +840,6 @@
           <t>Explore how haiku poems are structured/ discuss poems and express personal opinions/ Choose quotations to supportbyour esplanations.</t>
         </is>
       </c>
-      <c r="C35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -886,7 +852,6 @@
           <t>Explore how modern poets have used the ancient haiku form./ Look carefully at the natural world to help write your own haiku poem./ Use images and symbols to improve your poetic writing.</t>
         </is>
       </c>
-      <c r="C36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -899,7 +864,6 @@
           <t>Summarise information from an informative article./ Explore how writers use topics to organise texts./ Use prefixes to widen your vocabulary.</t>
         </is>
       </c>
-      <c r="C37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -912,7 +876,6 @@
           <t>Plan an interview to find out interesting onformation./ Explore the structure of a non-fection interview text./ Plan and write about a topic using specialist vocabulary.</t>
         </is>
       </c>
-      <c r="C38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -925,7 +888,6 @@
           <t>Check your progress 4</t>
         </is>
       </c>
-      <c r="C39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -938,7 +900,6 @@
           <t>Unit 5 · Unusual education</t>
         </is>
       </c>
-      <c r="C40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -951,7 +912,6 @@
           <t>Explore and discuss different types of schools./ Identify how connectives are used for different purposes./ Use connectives in a formal written account.</t>
         </is>
       </c>
-      <c r="C41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -964,7 +924,6 @@
           <t>Learn about bias in texts./ Explore persuasive writing techniques./ perform a persuasive speech.</t>
         </is>
       </c>
-      <c r="C42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -977,7 +936,6 @@
           <t>Explore views and ideas in texts./ Plan and deliver a presentation using appropriate media./ Consider the appropriate register to use when writting in a specific context.</t>
         </is>
       </c>
-      <c r="C43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -990,7 +948,6 @@
           <t>Identify explicit and implicit informstion./ Read and unseed text aloud./ Located quotations to support a point.</t>
         </is>
       </c>
-      <c r="C44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -1003,7 +960,6 @@
           <t>Revise prefixes and practise dictionary skills./ Discuss and interpret ideas in a text./ Use colons for a specific reason.</t>
         </is>
       </c>
-      <c r="C45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -1016,7 +972,6 @@
           <t>Check your progress 5</t>
         </is>
       </c>
-      <c r="C46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -1029,7 +984,6 @@
           <t>Unit 6 · Life stories</t>
         </is>
       </c>
-      <c r="C47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -1042,7 +996,6 @@
           <t>Read an unfamiliar text aloud./ Explore how writers use symbols in their poems./ Consider how readers make choices about what they read.</t>
         </is>
       </c>
-      <c r="C48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -1055,7 +1008,6 @@
           <t>Explore the different ways writers create voices./ Create content for a particular audence. / Consider the effectiveness of a partner's writing.</t>
         </is>
       </c>
-      <c r="C49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -1068,7 +1020,6 @@
           <t>Exploring some features of atobiography./ Debate critical responses to a text./ Consider structure when writing a monologue.</t>
         </is>
       </c>
-      <c r="C50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -1081,7 +1032,6 @@
           <t>Consider how a writer builds up detail./ Explore how literaly and linguistic tecniquesceate effects. / Explore the contexts of a personal letter.</t>
         </is>
       </c>
-      <c r="C51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -1094,7 +1044,6 @@
           <t>Experiment with ways of reading aloud for impact./ Explore how writers combine different language techniques./ Structure a poem</t>
         </is>
       </c>
-      <c r="C52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -1107,7 +1056,6 @@
           <t>Explore the text structure of a speech./ Use using a range of features when writing a speech. Deliver a persuasive speech.</t>
         </is>
       </c>
-      <c r="C53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -1120,7 +1068,6 @@
           <t>Check your progress 6</t>
         </is>
       </c>
-      <c r="C54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -1133,7 +1080,6 @@
           <t>Unit 7 · The travel agency</t>
         </is>
       </c>
-      <c r="C55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -1146,7 +1092,6 @@
           <t>Make predictions about a story using language and image cues./ Explore the narrative events of a fantasy fiction text. / Respond imaginatively to a ficctiontext,</t>
         </is>
       </c>
-      <c r="C56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -1159,7 +1104,6 @@
           <t>Explore how persuasive language is used.</t>
         </is>
       </c>
-      <c r="C57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -1172,7 +1116,6 @@
           <t>Leran to use persuasive techniques in your own wrinting. / Practise a role play.</t>
         </is>
       </c>
-      <c r="C58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -1185,7 +1128,6 @@
           <t>Explore how writers use characters to develo themes./ Consider how writers present heroic characters./ Write an analysis of how a character is presented.</t>
         </is>
       </c>
-      <c r="C59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
@@ -1198,7 +1140,6 @@
           <t>Use the nmes of word classes accurately./ Investigate different grammatical structures./ Interpret information to predict how a story will end.</t>
         </is>
       </c>
-      <c r="C60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
@@ -1211,7 +1152,6 @@
           <t>Use different ways to work out unfamiliar words./ Consider the role of a secondadry character in a text. / Explore writing in a personal voice.</t>
         </is>
       </c>
-      <c r="C61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
@@ -1224,7 +1164,6 @@
           <t>Check your progress 7</t>
         </is>
       </c>
-      <c r="C62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
@@ -1237,7 +1176,6 @@
           <t>Unit 8 · In the city</t>
         </is>
       </c>
-      <c r="C63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
@@ -1250,7 +1188,6 @@
           <t>Explore the effect of sentence structures and punctuation./ Investigate the effects created by imagery and figurative language./ Explore how writers use language which appeals to the senses</t>
         </is>
       </c>
-      <c r="C64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
@@ -1263,7 +1200,6 @@
           <t>Look at how informative articles can be structured./ Wrete an informative article for a specific audience./ Adapt speech for a specific purpose</t>
         </is>
       </c>
-      <c r="C65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
@@ -1276,7 +1212,6 @@
           <t>Consider setting as a structural feature. / Explore how a writer creates atmosphere through setting./Consider how to use language precisely to crreate an effect.</t>
         </is>
       </c>
-      <c r="C66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
@@ -1289,7 +1224,6 @@
           <t>Findout the meanings of unfamiliar words./ Consider how writers use figurative language to describe settings./ Investigate how figurative language is used for effect in poetry.</t>
         </is>
       </c>
-      <c r="C67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
@@ -1302,7 +1236,6 @@
           <t>Explore the origins and meanings of words. Consider whether an article is biased. / Ague a point of a view in a debate.</t>
         </is>
       </c>
-      <c r="C68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
@@ -1315,7 +1248,6 @@
           <t>Explore the effect of different perspectives./ Practise summarising information./ Design a poster to convey specific information.</t>
         </is>
       </c>
-      <c r="C69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
@@ -1328,7 +1260,6 @@
           <t>Check your progress 8</t>
         </is>
       </c>
-      <c r="C70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
@@ -1341,7 +1272,6 @@
           <t>Unit 9 · Dangers of the sea</t>
         </is>
       </c>
-      <c r="C71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
@@ -1354,7 +1284,6 @@
           <t>Explore how writers present antagonists./ Consider figurative language in a narrative text. / Refine your ability to describe characters.</t>
         </is>
       </c>
-      <c r="C72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
@@ -1367,7 +1296,6 @@
           <t>learn how writers create victim figures./ Explore how writers control information in a story./ Analyse and interpret victim and villain figures.</t>
         </is>
       </c>
-      <c r="C73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
@@ -1380,7 +1308,6 @@
           <t>Analyse the structure of an informative article./ Read and interpret the content of an article./ research and deliver a presentation.</t>
         </is>
       </c>
-      <c r="C74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
@@ -1393,7 +1320,6 @@
           <t>Create a picture based on a classic text./ Read and interpret a modern retelling of a classic text./ Use dialogue in creative writing.</t>
         </is>
       </c>
-      <c r="C75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
@@ -1406,7 +1332,6 @@
           <t>Understand the content of a classic poem./ Explore the effect of setting in a classic poem./ Produce a soundscape of a classic poem.</t>
         </is>
       </c>
-      <c r="C76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
@@ -1419,7 +1344,6 @@
           <t>Interpret and comment on the key events of a poem./ Identify and analyse techniques used in poetry./ Discuss and evaluate views about a poem.</t>
         </is>
       </c>
-      <c r="C77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
@@ -1432,7 +1356,6 @@
           <t>Check your progress 9</t>
         </is>
       </c>
-      <c r="C78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
@@ -1445,7 +1368,6 @@
           <t>Practice Exam 3</t>
         </is>
       </c>
-      <c r="C79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
@@ -1458,7 +1380,6 @@
           <t>Mock Exam.</t>
         </is>
       </c>
-      <c r="C80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
@@ -1468,10 +1389,9 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Review exam3</t>
-        </is>
-      </c>
-      <c r="C81" t="inlineStr"/>
+          <t>Review exam 3</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
@@ -1484,7 +1404,6 @@
           <t>Exam 3</t>
         </is>
       </c>
-      <c r="C82" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
